--- a/test/测试用例_罗盛哲.xlsx
+++ b/test/测试用例_罗盛哲.xlsx
@@ -3802,35 +3802,407 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-    </row>
-    <row r="12" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
+    <row r="7" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-006</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（create_base）</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">创建同名知识库（忽略大小写）时拒绝</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已存在一个 active 且 name 为 "CourseKB" 的知识库</t>
+        </is>
+      </c>
+      <c r="H7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name 为 "coursekb"（仅大小写不同），namespace 为 "default"</t>
+        </is>
+      </c>
+      <c r="I7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.create_base(session, {"name": "coursekb", "namespace": "default"}, "1")</t>
+        </is>
+      </c>
+      <c r="J7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">抛出 HTTPException，状态码 409，detail.code 为 KB_NAME_EXISTS，且未调用 session.add</t>
+        </is>
+      </c>
+      <c r="K7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M7" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值测试，验证同名（大小写不敏感）冲突校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-007</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（update_base）</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searchPolicyJson 为非对象时拒绝更新</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已存在知识库 kb-1（session mock 返回该 KB）</t>
+        </is>
+      </c>
+      <c r="H8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">searchPolicyJson 传入字符串 "vector"（非对象）</t>
+        </is>
+      </c>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.update_base(session, "kb-1", {"searchPolicyJson": "vector"})</t>
+        </is>
+      </c>
+      <c r="J8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">抛出 HTTPException，状态码 400，detail.code 为 INVALID_POLICY，且未提交事务</t>
+        </is>
+      </c>
+      <c r="K8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M8" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值测试，验证检索策略参数类型校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-008</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（archive_base）</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库归档与恢复生命周期</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已存在知识库 kb-1</t>
+        </is>
+      </c>
+      <c r="H9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">依次传入 archived=True 和 archived=False</t>
+        </is>
+      </c>
+      <c r="I9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先调用 archive_base(session, "kb-1", archived=True)，再调用 archive_base(session, "kb-1", archived=False)</t>
+        </is>
+      </c>
+      <c r="J9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">归档后 status 为 archived，恢复后 status 为 active，且 commit 共被调用 2 次</t>
+        </is>
+      </c>
+      <c r="K9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M9" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证归档与恢复的状态流转</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-009</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（list_bases）</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表查询是否包含归档项时过滤条件变化</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已 mock session 的 scalar 与 execute</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">include_archived 分别传入 False 和 True</t>
+        </is>
+      </c>
+      <c r="I10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分别调用 list_bases(active_session, include_archived=False) 和 list_bases(all_session, include_archived=True)</t>
+        </is>
+      </c>
+      <c r="J10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不包含归档时 SQL 含 te_knowledge_base.status 过滤条件，包含归档时不含该条件</t>
+        </is>
+      </c>
+      <c r="K10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">逻辑测试，验证归档过滤条件的拼接</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-010</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（分页）</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分页参数越界时被钳制到合理范围</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">page=0，page_size=101（越界值）</t>
+        </is>
+      </c>
+      <c r="I11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service._paginate_query(0, 101)</t>
+        </is>
+      </c>
+      <c r="J11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回 (1, 100)（页号最小 1、每页最大 100）</t>
+        </is>
+      </c>
+      <c r="K11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M11" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值测试，验证分页参数钳制逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-011</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（list_documents）</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档列表关键词过滤仅走元数据字段、不扫描正文</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已 mock session（scalar 返回 KB 与计数，execute 返回空结果）</t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyword="政策"，source_type="file"</t>
+        </is>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.list_documents(session, "kb-1", include_archived=False, keyword="政策", source_type="file")</t>
+        </is>
+      </c>
+      <c r="J12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询 SQL 含 title/source_ref/file_name/source_type/ingest_status 字段，不含 content_text 字段，且 items 为空列表</t>
+        </is>
+      </c>
+      <c r="K12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">性能相关逻辑测试，验证关键词搜索不扫描正文</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:140" x14ac:dyDescent="0.35">
       <c r="A13" s="39"/>

--- a/test/测试用例_罗盛哲.xlsx
+++ b/test/测试用例_罗盛哲.xlsx
@@ -4204,80 +4204,340 @@
         </is>
       </c>
     </row>
-    <row r="13" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-    </row>
-    <row r="14" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A14" s="39"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-    </row>
-    <row r="15" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-    </row>
-    <row r="16" spans="1:140" x14ac:dyDescent="0.35">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
+    <row r="13" spans="1:140" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-012</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库文档解析（extract_text_from_bytes）</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTF-8 编码文本提取无乱码</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文件名 "政策.txt"，MIME 类型 "text/plain"，内容 "武汉扶持政策"（UTF-8 编码）</t>
+        </is>
+      </c>
+      <c r="I13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 extract_text_from_bytes("政策.txt", "text/plain", "武汉扶持政策".encode("utf-8"))</t>
+        </is>
+      </c>
+      <c r="J13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回 title="政策.txt"、contentText="武汉扶持政策"、pages=0、metadata={}</t>
+        </is>
+      </c>
+      <c r="K13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M13" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证 UTF-8 文本解析无乱码</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:140" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-013</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库文档解析（extract_markdown_front_matter）</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markdown 元数据提取并剥离</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markdown 文本（含标题、地区/年份等元数据及正文）</t>
+        </is>
+      </c>
+      <c r="I14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 extract_markdown_front_matter(text)</t>
+        </is>
+      </c>
+      <c r="J14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title 为"测试政策"、metadata 含地区/年份/标题、contentText 为"正文内容"、sourceType 为 markdown_metadata_block</t>
+        </is>
+      </c>
+      <c r="K14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证 Markdown 元数据解析与剥离</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:140" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-014</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库文档解析（extract_text_from_bytes）</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不支持的二进制文件被拒绝</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文件名 "sample.exe"，MIME 类型 "application/octet-stream"，二进制内容</t>
+        </is>
+      </c>
+      <c r="I15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 extract_text_from_bytes("sample.exe", "application/octet-stream", b"binary")</t>
+        </is>
+      </c>
+      <c r="J15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">抛出 HTTPException，状态码 400，detail.code 为 UNSUPPORTED_FILE</t>
+        </is>
+      </c>
+      <c r="K15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值/异常场景测试，验证不支持文件类型的拒绝处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:140" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-015</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库切片（chunk_text）</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大小边界处生成单个切片</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">settings.chunk_size=100、chunk_overlap=0（经 monkeypatch 设置）</t>
+        </is>
+      </c>
+      <c r="H16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标题 "T"，内容为 97 个 "x"</t>
+        </is>
+      </c>
+      <c r="I16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.chunk_text("T", content)</t>
+        </is>
+      </c>
+      <c r="J16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回单个切片（标题 T 加两个换行再加正文），切片长度为 100</t>
+        </is>
+      </c>
+      <c r="K16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M16" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值测试，验证切片大小边界（97+3=100 不超限）的切分逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:140" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-016</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库管理（update_base）</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库重命名为已存在名称时未被拒绝（缺陷）</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已存在知识库 A（name=A）与知识库 B（name=B），均为 active</t>
+        </is>
+      </c>
+      <c r="H17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对 B 传入 name="A"（重命名为已存在的名称）</t>
+        </is>
+      </c>
+      <c r="I17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.update_base(session, "kb-b", {"name": "A"})</t>
+        </is>
+      </c>
+      <c r="J17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预期抛出 HTTPException，状态码 409，detail.code 为 KB_NAME_EXISTS</t>
+        </is>
+      </c>
+      <c r="K17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未抛出异常，重命名直接成功（DID NOT RAISE），导致两个 active 知识库同名</t>
+        </is>
+      </c>
+      <c r="L17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NG</t>
+        </is>
+      </c>
+      <c r="M17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【缺陷】update_base 缺少重名冲突校验（create_base 有、update_base 没有），导致知识库可被重命名为已存在的同名知识库，需补充同名（大小写不敏感）检查</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="39"/>

--- a/test/测试用例_罗盛哲.xlsx
+++ b/test/测试用例_罗盛哲.xlsx
@@ -4539,80 +4539,340 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="39"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="39"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="39"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
+    <row r="18" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-017</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库文档解析（extract_text_from_bytes）</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GB18030 编码文本提取无乱码</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文件名 "通知.txt"，MIME 类型 "text/plain"，内容 "武汉园区通知"（GB18030 编码）</t>
+        </is>
+      </c>
+      <c r="I18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 extract_text_from_bytes("通知.txt", "text/plain", "武汉园区通知".encode("gb18030"))</t>
+        </is>
+      </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回 contentText="武汉园区通知"、pages=0，中文字符无乱码</t>
+        </is>
+      </c>
+      <c r="K18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证 GB18030 编码文本解析无乱码</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-018</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库文档解析（extract_markdown_front_matter）</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YAML front matter 元数据提取并剥离</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markdown 文本（--- title: 测试通知 / region: 武汉 --- 正文内容），配置 enabled=True、format="yaml_front_matter"、stripExtractedBlock=True</t>
+        </is>
+      </c>
+      <c r="I19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 extract_markdown_front_matter(text, {"enabled": True, "format": "yaml_front_matter", "stripExtractedBlock": True})</t>
+        </is>
+      </c>
+      <c r="J19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回 metadata={"title": "测试通知", "region": "武汉"}、contentText="正文内容"、sourceType="yaml_front_matter"</t>
+        </is>
+      </c>
+      <c r="K19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证 YAML front matter 解析与原文块剥离</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-019</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库元数据（parse_metadata）</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">元数据为非对象 JSON 数组时被拒绝</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字符串 '["not", "an", "object"]'（JSON 数组，非 JSON 对象）</t>
+        </is>
+      </c>
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 parse_metadata('["not", "an", "object"]')</t>
+        </is>
+      </c>
+      <c r="J20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">抛出 HTTPException，状态码 400，detail.code 为 INVALID_METADATA</t>
+        </is>
+      </c>
+      <c r="K20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值/异常场景测试，验证元数据必须是 JSON 对象而非数组</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-020</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库元数据（normalize_metadata）</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">元数据按 mappings 做类型转换并套用 defaults</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无</t>
+        </is>
+      </c>
+      <c r="H21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原始元数据 {"地区":"武汉","支持方式":"补贴；贷款","有效":"是","备注":"公开"}；extraction_config 含 mappings（string/list/boolean 三类）、defaults={"common.year":2026}、keepUnmappedInDomain=True</t>
+        </is>
+      </c>
+      <c r="I21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 normalize_metadata(原始元数据, file_name="政策.md", extraction_config=config)</t>
+        </is>
+      </c>
+      <c r="J21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">common={"region":"武汉","year":2026}；domain.supportModes=["补贴","贷款"]；domain.active=True；domain.备注="公开"；_ingest.fileName="政策.md"</t>
+        </is>
+      </c>
+      <c r="K21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正常功能测试，验证元数据映射的类型转换、默认值填充与未映射字段保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-KB-021</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">知识库切片（chunk_text）</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多切片之间产生重叠内容</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="F22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+      <c r="G22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">settings.chunk_size=100、chunk_overlap=10（经 monkeypatch 设置）</t>
+        </is>
+      </c>
+      <c r="H22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标题 ""（空标题），内容为 150 个 "x"</t>
+        </is>
+      </c>
+      <c r="I22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调用 kb_service.chunk_text("", content)</t>
+        </is>
+      </c>
+      <c r="J22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返回 2 个切片，且第 2 个切片以 10 个 "x" 加两个换行开头</t>
+        </is>
+      </c>
+      <c r="K22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">与预期一致</t>
+        </is>
+      </c>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="M22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界值测试，验证切片重叠（chunk_overlap=10）在相邻切片间生效</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="39"/>
